--- a/Versão5/EST/Ontologia_Metalica.xlsx
+++ b/Versão5/EST/Ontologia_Metalica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\META\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DC97FE-0E77-461A-AAD3-CD7173F94FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B229E20E-A113-465D-AD3B-1B529CE0B845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -3854,6 +3854,14 @@
   <dxfs count="7">
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3871,14 +3879,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4236,15 +4236,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="51" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="51" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -4433,19 +4433,19 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46244.637201736114</v>
+        <v>46249.395712847225</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="51" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="51" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>1007</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>1070</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>1072</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>1074</v>
       </c>
@@ -4559,40 +4559,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA126"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.69140625" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="146.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="156.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.42578125" style="38" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="134" style="38" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="59.5703125" style="38" customWidth="1"/>
-    <col min="29" max="16384" width="2.7109375" style="38"/>
+    <col min="1" max="1" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.53515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.53515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.23046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.15234375" style="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.53515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="108.4609375" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="115.23046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.84375" style="38" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.61328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.53515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.921875" style="38" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" style="38" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="99.15234375" style="38" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="59.53515625" style="38" customWidth="1"/>
+    <col min="29" max="16384" width="2.69140625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="30.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24">
         <v>0</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="63">
         <v>2</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>Alloy steel used in the project</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="63">
         <v>3</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>Aluminum alloys used in the project</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="63">
         <v>4</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>Rebar for reinforced concrete.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="63">
         <v>5</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>Smooth rebar for reinforced concrete. Generally used when adhesion is not a primary concern, such as on slabs and floors. Can be in CA-25 Steel.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63">
         <v>6</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>Ribbed rebar for reinforced concrete. They have protrusions along their surface, with superior adhesion to concrete. Used in structural elements subject to high loads, such as beams and columns. They can be produced in CA-50, CA-60 and CA-70 Steel.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="63">
         <v>7</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>Rebar produced by Gerdau. The GG 70 stands out as a high-performance solution that redefines structural standards, offering more strength, productivity and resource rationalization. It is made of CA-70 Steel.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="63">
         <v>8</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>Stirrup to resist cutting forces and keep rebar in position. They ensure even distribution of efforts.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="63">
         <v>9</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>Stirrup used in circular formwork and pipes.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63">
         <v>10</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>Stirrup that increases resistance against diagonal forces in beams and columns.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="63">
         <v>11</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>Stirrup used in structures subject to high torsional stress.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="63">
         <v>12</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>Made of ribbed CA-60 steel and GG-50 steel. Ribbed Welded Mesh is supplied in panels and formed by welded wires or bars at all crossing points configuring the cracking control mesh and mechanical resistance.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="63">
         <v>13</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>Welded ready reinforcement (APS). Delivered ready at the site, according to the project of the work. The pieces are delivered identified and according to the schedule of execution of the work.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="63">
         <v>14</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>Built-in formwork is produced with 0.5 mm thick galvanized steel panels with perforations, delivered with plastic spacers and galvanized clamps for permanent application that replaces the temporary conventional formwork, eliminating the formwork step.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="63">
         <v>15</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>Built-in formwork mounted with welded ready reinforcement (APS).</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63">
         <v>16</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>Welded metal profile for Column and Beam (CVS). They are structural metal profiles formed by joining steel plates connected with welding.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="63">
         <v>17</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>Welded metal profile for Column (CS). They are structural metal profiles formed by joining steel plates connected with welding.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="63">
         <v>18</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>Welded metal profile for Beams (VS). They are structural metal profiles formed by joining steel plates connected with welding.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="63">
         <v>19</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>Hot-rolled profile made of heated steel and shaped by industrial rollers in I-shape with parallel flaps with lengths from 6 to 12 m.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="63">
         <v>20</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>Hot-rolled profile made of heated steel and shaped by industrial rollers in HP format with parallel flaps with lengths from 6 to 12 m.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="63">
         <v>21</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>Hot-rolled profile made of heated steel and shaped by W-shaped industrial rollers with parallel flaps with lengths from 6 to 12 m.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="63">
         <v>22</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>Hot-rolled profile of heated steel and shaped by industrial rollers in L shape with equal flaps.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="63">
         <v>23</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>Hot-rolled profile of heated steel and shaped by industrial rollers in L shape with uneven flaps.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="63">
         <v>24</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>Hot-rolled profile of steel heated and shaped by industrial rollers in S-format (Sigma).</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="63">
         <v>25</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>Hot-rolled profile of heated steel and shaped by industrial T-shaped rollers.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="63">
         <v>26</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>Hot-rolled profile of steel heated and molded by industrial U-shaped rollers.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="63">
         <v>27</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>Hot-rolled profile of heated steel and shaped by hardened U-shaped industrial rollers.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="63">
         <v>28</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>Hot-rolled profile of heated steel and shaped by industrial rollers in Z shape.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="63">
         <v>29</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>Circular section tubular profile.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="63">
         <v>30</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>Square section tubular profile.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="63">
         <v>31</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>Tubular profile with rectangular section.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="63">
         <v>32</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>Base Plate</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="63">
         <v>33</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>Steel-concrete interface plate</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="63">
         <v>34</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>Steel-concrete interface plate</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="63">
         <v>35</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>Splice plate for joining metal parts</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="63">
         <v>36</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>Plate for closure</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="63">
         <v>37</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>Plate to connect the column and the girder of the gantry of a metal shed.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="63">
         <v>38</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>Plate to connect the gantry beams of a metal shed.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="63">
         <v>39</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>Gusset plate is used to connect diagonal bars, uprights and flanges in metal truss nodes.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="63">
         <v>40</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>SteelDeck system for high-strength slab, consisting of a trapezoidal profiled steel sheet as a concrete formwork. ZAR 280 steel. Thicknesses of 0.8 mm, 0.95 and 1.25 mm. Length 12 m, Cover width 0.85 m.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="63">
         <v>41</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>Round Rolled Bar</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="63">
         <v>42</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>Square Rolled Bar</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="63">
         <v>43</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>Hexagonal Rolled Bar</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="63">
         <v>44</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>Flat bar</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="63">
         <v>45</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>Drawn round bar</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="63">
         <v>46</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>Drawn square bar</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="63">
         <v>47</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>Drawn round bar</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="63">
         <v>48</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>Bar of a bracing.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="63">
         <v>49</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>Compressed bar of a bracing.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="63">
         <v>50</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>Traction bar of a bracing.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="63">
         <v>51</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>Slash upstream a structure.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="63">
         <v>52</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>Diagonal bar a structure.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="63">
         <v>53</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>Top sting of a truss.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="63">
         <v>54</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>Lower flange of a truss.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="63">
         <v>55</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>Horizontal Diagonal Bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="63">
         <v>56</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>Horizontal Cross Bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="63">
         <v>57</v>
       </c>
@@ -9831,7 +9831,7 @@
         <v>Horizontal bracing K. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="63">
         <v>58</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>Horizontal V bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="63">
         <v>59</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>Horizontal inverted V bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="63">
         <v>60</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>Horizontal Delta bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="63">
         <v>61</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>Vertical Diagonal Bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="63">
         <v>62</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>Vertical Cross Bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="63">
         <v>63</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>Vertical K bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="63">
         <v>64</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>Vertical V bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="63">
         <v>65</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>Vertical inverted V bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="63">
         <v>66</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>Horizontal Delta bracing. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="63">
         <v>67</v>
       </c>
@@ -10751,7 +10751,7 @@
         <v>Bracing with tensioned cable. Bracing increases the overall rigidity of the metal structure and helps reduce the weight and efficiency of the parts.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="63">
         <v>68</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>Truss of parallel flanges with diagonals sloping downwards towards the center.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="63">
         <v>69</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>Truss of parallel flanges with diagonals sloping upwards towards the center.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="63">
         <v>70</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>Lattice of parallel flanges with diagonals forming equilateral or isosceles triangles.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="63">
         <v>71</v>
       </c>
@@ -11119,7 +11119,7 @@
         <v>Truss with sloping flanges with W or M diagonals.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="63">
         <v>72</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>Truss with greater height and no diagonals. Formed by rigid rectacles or squares.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="63">
         <v>73</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>Flat truss of sloping flanges for residential roofs.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="63">
         <v>74</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>Flat truss with parallel flanges for bridges.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="63">
         <v>75</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>Spatial truss formed by two or more layers of equal bars arranged in a square or rectangular mesh.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="63">
         <v>76</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>Spatial truss formed as a geodesic dome of equilateral or near-equilateral triangles.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="63">
         <v>77</v>
       </c>
@@ -11671,7 +11671,7 @@
         <v>Spatial truss formed as a vault or curvatures of equilateral or near-equilateral tricculles.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="63">
         <v>78</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>Spatial truss formed by pyramidal spatial modules of equal bars.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="63">
         <v>79</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>Spatial truss formed by spatial modules of octahedra of equal bars.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="63">
         <v>80</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>Truss of space modules of mixed formation of equal bars.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="63">
         <v>81</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>Anchoring element</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="63">
         <v>82</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>Connector element</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="63">
         <v>83</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>Estai Anchoring</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="63">
         <v>84</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>Anchor Coupler</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="63">
         <v>85</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>Fixed Extreme Anchorage</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="63">
         <v>86</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>Extreme Tensioned Anchor</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="63">
         <v>87</v>
       </c>
@@ -12591,7 +12591,7 @@
         <v>Stay</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="63">
         <v>88</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>Tensioner Bar</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="63">
         <v>89</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>Coated Tensioner</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="63">
         <v>90</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>Tensioner Sheath</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="63">
         <v>91</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>Tensioner Sheath Coupler</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="63">
         <v>92</v>
       </c>
@@ -13051,7 +13051,7 @@
         <v>Diabolo Sheath Tensioner</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="63">
         <v>93</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>Tensioner Sheath Cable</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="63">
         <v>94</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>Injector Tensioner</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="63">
         <v>95</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>Trumpet Tensor</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="63">
         <v>96</v>
       </c>
@@ -13419,7 +13419,7 @@
         <v>Rope Tensioner</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="63">
         <v>97</v>
       </c>
@@ -13511,7 +13511,7 @@
         <v>Wire Tensioner</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="63">
         <v>98</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>Structural Mast</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="63">
         <v>99</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>Closure membrane</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="63">
         <v>100</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>Purlins for metal structure roofing placed at 1.50 m to support the roof.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="63">
         <v>101</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>Purlins to support façade elements placed at 1.50 m to support vertical panels.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="63">
         <v>102</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>Purlins to support façade elements placed at 1.50 m to support vertical panels.</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="63">
         <v>103</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>Metal connection at the junction between the inclined beam (rafter) and the vertical column at the point where the roof meets the side wall.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="63">
         <v>104</v>
       </c>
@@ -14155,7 +14155,7 @@
         <v>Metal connection at the junction between the inclined beam (rafter) and the purlin.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="63">
         <v>105</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>Metal connection at the junction between the inclined beams of the gantry.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="63">
         <v>106</v>
       </c>
@@ -14339,7 +14339,7 @@
         <v>Alignment of purliners.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="63">
         <v>107</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>Sandwich panel for facades with PIR AP cores covered by pre-painted steel sheets. They provide architectural finish with a concealed fitting system. Manufactured with high-pressure foam injection, they ensure uniformity of insulation.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="63">
         <v>108</v>
       </c>
@@ -14523,7 +14523,7 @@
         <v>Thermal Panel with EPS core meets thermal insulation demands in environments that require strict temperature control, such as refrigerators and cold rooms.</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="63">
         <v>109</v>
       </c>
@@ -14615,7 +14615,7 @@
         <v>Zipped sandwich tile system is applied to roofs with low slope and large areas, offering thermal insulation and watertightness without the need for drilling.</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="63">
         <v>110</v>
       </c>
@@ -14707,7 +14707,7 @@
         <v>Corrugated Roofing Sheet composed of layers of Galvalume steel and PIR core, with excellent thermal insulation and weather resistance, for residential and commercial projects.</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="63">
         <v>111</v>
       </c>
@@ -14799,7 +14799,7 @@
         <v>Isothermal trapezoidal sandwich tile offers thermal comfort and energy saving. With three trapezoids, it has great mechanical resistance, ideal for roofs that require greater spacing between purlins, helping to reduce the support structure.</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="63">
         <v>112</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>Isothermal trapezoidal sandwich tile offers thermal comfort and energy saving. With trapezoids of adapted shape for the placement of solar panels integrated into the roof.</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="63">
         <v>113</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>Trapezoidal Tile</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="63">
         <v>114</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>Corrugated Roofing Sheet composed of layers of Galvalume steel and PIR core, with excellent thermal insulation and weather resistance, for residential and commercial projects.</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="63">
         <v>115</v>
       </c>
@@ -15167,7 +15167,7 @@
         <v>Sandwich zipped tile system is applied to roofs with low slope and large areas, offering thermal insulation and watertightness without the need for drilling.</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="63">
         <v>116</v>
       </c>
@@ -15259,7 +15259,7 @@
         <v>Anchor bolt located in the inner region of the base plate</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="63">
         <v>117</v>
       </c>
@@ -15351,7 +15351,7 @@
         <v>Anchor bolt located in the outer region of the base plate</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="63">
         <v>118</v>
       </c>
@@ -15443,7 +15443,7 @@
         <v>DIN standard structural bolt</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="63">
         <v>119</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>ASTM Heavy Duty Thread Structural Bolt</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="63">
         <v>120</v>
       </c>
@@ -15627,7 +15627,7 @@
         <v>Drywall Screw</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="63">
         <v>121</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>Drilling Screw</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="63">
         <v>122</v>
       </c>
@@ -15811,7 +15811,7 @@
         <v>Self-tapping screw</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="63">
         <v>123</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>Shear Pin for Steel Deck Slabs</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="63">
         <v>124</v>
       </c>
@@ -15995,7 +15995,7 @@
         <v>Metal shed</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="63">
         <v>125</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>Metal shed of multiple modules.</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="63">
         <v>126</v>
       </c>
@@ -16197,14 +16197,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="22"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -16269,7 +16269,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -16343,16 +16343,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.3046875" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -16380,7 +16380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -16403,49 +16403,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AK156"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="68" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="68" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="68" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="68" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="68" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" style="70" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="70" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="68" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.53515625" style="68" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.84375" style="68" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" style="68" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.3828125" style="68" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.84375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.84375" style="69" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" style="69" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.3828125" style="70" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.69140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" style="70" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="69" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.5703125" style="69" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.53515625" style="69" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.84375" style="71" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="3" style="69" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.15234375" style="69" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.84375" style="71" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="68" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="109.85546875" style="68" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="94.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" style="69" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.7109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.42578125" style="69" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.42578125" style="69" customWidth="1"/>
-    <col min="36" max="36" width="7.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.7109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="68"/>
+    <col min="29" max="29" width="109.84375" style="68" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="94.15234375" style="69" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.3828125" style="69" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.69140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.3828125" style="69" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.3828125" style="69" customWidth="1"/>
+    <col min="36" max="36" width="7.3046875" style="69" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.69140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.15234375" style="68"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -16671,7 +16671,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -16784,7 +16784,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17010,7 +17010,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17123,7 +17123,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -18253,7 +18253,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -18479,7 +18479,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -18592,7 +18592,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -18705,7 +18705,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -18931,7 +18931,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -19044,7 +19044,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -19157,7 +19157,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -19270,7 +19270,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -19383,7 +19383,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -19496,7 +19496,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -19948,7 +19948,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -20061,7 +20061,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -20287,7 +20287,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -20400,7 +20400,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -20513,7 +20513,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -20626,7 +20626,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -20852,7 +20852,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -20965,7 +20965,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -21191,7 +21191,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -21417,7 +21417,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -21530,7 +21530,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -21643,7 +21643,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -21869,7 +21869,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -21982,7 +21982,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -22208,7 +22208,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="52" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -22321,7 +22321,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -22547,7 +22547,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -22660,7 +22660,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="56" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -22773,7 +22773,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="57" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -22999,7 +22999,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="59" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -23112,7 +23112,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="60" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -23225,7 +23225,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="61" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="62" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="16">
         <v>62</v>
       </c>
@@ -23451,7 +23451,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="63" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="16">
         <v>63</v>
       </c>
@@ -23564,7 +23564,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="64" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="16">
         <v>64</v>
       </c>
@@ -23677,7 +23677,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="65" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="16">
         <v>65</v>
       </c>
@@ -23790,7 +23790,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="66" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="16">
         <v>66</v>
       </c>
@@ -23903,7 +23903,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="67" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="16">
         <v>67</v>
       </c>
@@ -24016,7 +24016,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="68" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="16">
         <v>68</v>
       </c>
@@ -24129,7 +24129,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="69" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="16">
         <v>69</v>
       </c>
@@ -24242,7 +24242,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="70" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="16">
         <v>70</v>
       </c>
@@ -24355,7 +24355,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="71" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="16">
         <v>71</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="72" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="16">
         <v>72</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="73" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="16">
         <v>73</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="74" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="16">
         <v>74</v>
       </c>
@@ -24807,7 +24807,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="75" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="16">
         <v>75</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="76" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="16">
         <v>76</v>
       </c>
@@ -25033,7 +25033,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="77" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="16">
         <v>77</v>
       </c>
@@ -25146,7 +25146,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="78" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="16">
         <v>78</v>
       </c>
@@ -25259,7 +25259,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="79" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="16">
         <v>79</v>
       </c>
@@ -25372,7 +25372,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="80" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="16">
         <v>80</v>
       </c>
@@ -25485,7 +25485,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="81" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="16">
         <v>81</v>
       </c>
@@ -25598,7 +25598,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="82" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="16">
         <v>82</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="83" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="16">
         <v>83</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="84" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16">
         <v>84</v>
       </c>
@@ -25937,7 +25937,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="85" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="16">
         <v>85</v>
       </c>
@@ -26050,7 +26050,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="86" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="16">
         <v>86</v>
       </c>
@@ -26163,7 +26163,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="87" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16">
         <v>87</v>
       </c>
@@ -26276,7 +26276,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="88" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16">
         <v>88</v>
       </c>
@@ -26389,7 +26389,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="89" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16">
         <v>89</v>
       </c>
@@ -26502,7 +26502,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="90" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16">
         <v>90</v>
       </c>
@@ -26615,7 +26615,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="91" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16">
         <v>91</v>
       </c>
@@ -26728,7 +26728,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="92" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16">
         <v>92</v>
       </c>
@@ -26841,7 +26841,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="93" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16">
         <v>93</v>
       </c>
@@ -26954,7 +26954,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="94" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16">
         <v>94</v>
       </c>
@@ -27067,7 +27067,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="95" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="16">
         <v>95</v>
       </c>
@@ -27180,7 +27180,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="96" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="16">
         <v>96</v>
       </c>
@@ -27293,7 +27293,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="97" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16">
         <v>97</v>
       </c>
@@ -27406,7 +27406,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="98" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16">
         <v>98</v>
       </c>
@@ -27519,7 +27519,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="99" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16">
         <v>99</v>
       </c>
@@ -27632,7 +27632,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="100" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16">
         <v>100</v>
       </c>
@@ -27745,7 +27745,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="101" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16">
         <v>101</v>
       </c>
@@ -27858,7 +27858,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="102" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16">
         <v>102</v>
       </c>
@@ -27971,7 +27971,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="103" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="16">
         <v>103</v>
       </c>
@@ -28084,7 +28084,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="104" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="16">
         <v>104</v>
       </c>
@@ -28197,7 +28197,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="105" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="16">
         <v>105</v>
       </c>
@@ -28310,7 +28310,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="106" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="16">
         <v>106</v>
       </c>
@@ -28423,7 +28423,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="107" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="16">
         <v>107</v>
       </c>
@@ -28536,7 +28536,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="108" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="16">
         <v>108</v>
       </c>
@@ -28649,7 +28649,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="109" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="16">
         <v>109</v>
       </c>
@@ -28762,7 +28762,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="110" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="16">
         <v>110</v>
       </c>
@@ -28875,7 +28875,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="111" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="16">
         <v>111</v>
       </c>
@@ -28988,7 +28988,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="112" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="16">
         <v>112</v>
       </c>
@@ -29101,7 +29101,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="113" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="16">
         <v>113</v>
       </c>
@@ -29214,7 +29214,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="114" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="16">
         <v>114</v>
       </c>
@@ -29327,7 +29327,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="115" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="16">
         <v>115</v>
       </c>
@@ -29440,7 +29440,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="116" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="16">
         <v>116</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="117" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="16">
         <v>117</v>
       </c>
@@ -29666,7 +29666,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="118" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="16">
         <v>118</v>
       </c>
@@ -29779,7 +29779,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="119" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="16">
         <v>119</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="120" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="16">
         <v>120</v>
       </c>
@@ -30005,7 +30005,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="121" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="16">
         <v>121</v>
       </c>
@@ -30118,7 +30118,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="122" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="16">
         <v>122</v>
       </c>
@@ -30231,7 +30231,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="123" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="16">
         <v>123</v>
       </c>
@@ -30344,7 +30344,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="124" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="16">
         <v>124</v>
       </c>
@@ -30457,7 +30457,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="125" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="16">
         <v>125</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="126" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="16">
         <v>126</v>
       </c>
@@ -30683,7 +30683,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="127" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="16">
         <v>127</v>
       </c>
@@ -30796,7 +30796,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="128" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="16">
         <v>128</v>
       </c>
@@ -30909,7 +30909,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="129" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="16">
         <v>129</v>
       </c>
@@ -31022,7 +31022,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="130" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="16">
         <v>130</v>
       </c>
@@ -31135,7 +31135,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="131" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="16">
         <v>131</v>
       </c>
@@ -31248,7 +31248,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="132" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="16">
         <v>132</v>
       </c>
@@ -31361,7 +31361,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="133" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="16">
         <v>133</v>
       </c>
@@ -31474,7 +31474,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="134" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="16">
         <v>134</v>
       </c>
@@ -31587,7 +31587,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="135" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="16">
         <v>135</v>
       </c>
@@ -31700,7 +31700,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="136" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="16">
         <v>136</v>
       </c>
@@ -31813,7 +31813,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="137" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="16">
         <v>137</v>
       </c>
@@ -31926,7 +31926,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="138" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="16">
         <v>138</v>
       </c>
@@ -32039,7 +32039,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="139" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="16">
         <v>139</v>
       </c>
@@ -32152,7 +32152,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="140" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="16">
         <v>140</v>
       </c>
@@ -32265,7 +32265,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="141" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="16">
         <v>141</v>
       </c>
@@ -32378,7 +32378,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="142" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="16">
         <v>142</v>
       </c>
@@ -32491,7 +32491,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="143" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="16">
         <v>143</v>
       </c>
@@ -32604,7 +32604,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="144" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="16">
         <v>144</v>
       </c>
@@ -32717,7 +32717,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="145" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="16">
         <v>145</v>
       </c>
@@ -32830,7 +32830,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="146" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="16">
         <v>148</v>
       </c>
@@ -32943,7 +32943,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="147" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="16">
         <v>149</v>
       </c>
@@ -33056,7 +33056,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="148" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="16">
         <v>150</v>
       </c>
@@ -33169,7 +33169,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="149" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="16">
         <v>151</v>
       </c>
@@ -33282,7 +33282,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="150" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="16">
         <v>152</v>
       </c>
@@ -33395,7 +33395,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="151" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="16">
         <v>153</v>
       </c>
@@ -33508,7 +33508,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="152" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="16">
         <v>154</v>
       </c>
@@ -33621,7 +33621,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="153" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="16">
         <v>155</v>
       </c>
@@ -33734,7 +33734,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="154" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="16">
         <v>156</v>
       </c>
@@ -33847,7 +33847,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="155" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="16">
         <v>157</v>
       </c>
@@ -33960,7 +33960,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="156" spans="1:37" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:37" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="16">
         <v>158</v>
       </c>
@@ -34075,18 +34075,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B156">
+    <cfRule type="duplicateValues" dxfId="4" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="476"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF12 AH4:AH12 AJ4:AK12">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B156">
-    <cfRule type="duplicateValues" dxfId="1" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="476"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/EST/Ontologia_Metalica.xlsx
+++ b/Versão5/EST/Ontologia_Metalica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2FC47-5979-42E7-B053-AAE8B1A26802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293147A5-E39A-4574-B8DF-32DA46E9C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -5173,15 +5173,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="46" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="46" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -5370,19 +5370,19 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46260.352568287039</v>
+        <v>46264.567174884258</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="46" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="46" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>1000</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>1059</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>1061</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>1063</v>
       </c>
@@ -5496,42 +5496,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC146"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.69140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="35" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.15234375" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.3828125" style="35" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3828125" style="35" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="35" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="42.140625" style="35" customWidth="1"/>
-    <col min="17" max="17" width="49.5703125" style="35" customWidth="1"/>
-    <col min="18" max="18" width="42.85546875" style="35" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.15234375" style="35" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.15234375" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.53515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="42.15234375" style="35" customWidth="1"/>
+    <col min="17" max="17" width="49.53515625" style="35" customWidth="1"/>
+    <col min="18" max="18" width="42.84375" style="35" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.15234375" style="35" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.15234375" style="35" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.3828125" style="35" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.3828125" style="35" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.3046875" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="59.5703125" style="35" customWidth="1"/>
-    <col min="31" max="16384" width="2.7109375" style="35"/>
+    <col min="29" max="29" width="4.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="59.53515625" style="35" customWidth="1"/>
+    <col min="31" max="16384" width="2.69140625" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24">
         <v>0</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="55">
         <v>28</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="55">
         <v>29</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="55">
         <v>30</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="55">
         <v>31</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="55">
         <v>32</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="55">
         <v>33</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="55">
         <v>34</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="55">
         <v>35</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="55">
         <v>36</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="55">
         <v>37</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="55">
         <v>38</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="55">
         <v>39</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="55">
         <v>40</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="55">
         <v>41</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="55">
         <v>42</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="55">
         <v>43</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="55">
         <v>44</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="55">
         <v>45</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="55">
         <v>46</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="55">
         <v>47</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="55">
         <v>48</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="55">
         <v>49</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="55">
         <v>50</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="55">
         <v>51</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="55">
         <v>52</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="55">
         <v>53</v>
       </c>
@@ -10668,7 +10668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="55">
         <v>54</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="55">
         <v>55</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="55">
         <v>56</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="55">
         <v>57</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="55">
         <v>58</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="55">
         <v>59</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="55">
         <v>60</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="55">
         <v>61</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="55">
         <v>62</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="55">
         <v>63</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="55">
         <v>64</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="55">
         <v>65</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="55">
         <v>66</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="55">
         <v>67</v>
       </c>
@@ -12026,7 +12026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="55">
         <v>68</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="55">
         <v>69</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="55">
         <v>70</v>
       </c>
@@ -12317,7 +12317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="55">
         <v>71</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="55">
         <v>72</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="55">
         <v>73</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="55">
         <v>74</v>
       </c>
@@ -12705,7 +12705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="55">
         <v>75</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="55">
         <v>76</v>
       </c>
@@ -12899,7 +12899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="55">
         <v>77</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="55">
         <v>78</v>
       </c>
@@ -13093,7 +13093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="55">
         <v>79</v>
       </c>
@@ -13190,7 +13190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="55">
         <v>80</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="55">
         <v>81</v>
       </c>
@@ -13384,7 +13384,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="55">
         <v>82</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="55">
         <v>83</v>
       </c>
@@ -13578,7 +13578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="55">
         <v>84</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="55">
         <v>85</v>
       </c>
@@ -13772,7 +13772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="55">
         <v>86</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="55">
         <v>87</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="55">
         <v>88</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="55">
         <v>89</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="55">
         <v>90</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="55">
         <v>91</v>
       </c>
@@ -14354,7 +14354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="55">
         <v>92</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="55">
         <v>93</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="55">
         <v>94</v>
       </c>
@@ -14645,7 +14645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="55">
         <v>95</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="55">
         <v>96</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="55">
         <v>97</v>
       </c>
@@ -14936,7 +14936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="55">
         <v>98</v>
       </c>
@@ -15033,7 +15033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="55">
         <v>99</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="55">
         <v>100</v>
       </c>
@@ -15227,7 +15227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="55">
         <v>101</v>
       </c>
@@ -15324,7 +15324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="55">
         <v>102</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="55">
         <v>103</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="55">
         <v>104</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="55">
         <v>105</v>
       </c>
@@ -15712,7 +15712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="55">
         <v>106</v>
       </c>
@@ -15809,7 +15809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="55">
         <v>107</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="55">
         <v>108</v>
       </c>
@@ -16003,7 +16003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="55">
         <v>109</v>
       </c>
@@ -16100,7 +16100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="55">
         <v>110</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="55">
         <v>111</v>
       </c>
@@ -16294,7 +16294,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="55">
         <v>112</v>
       </c>
@@ -16391,7 +16391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="55">
         <v>113</v>
       </c>
@@ -16488,7 +16488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="55">
         <v>114</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="55">
         <v>115</v>
       </c>
@@ -16682,7 +16682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="55">
         <v>116</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="55">
         <v>117</v>
       </c>
@@ -16876,7 +16876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="55">
         <v>118</v>
       </c>
@@ -16973,7 +16973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="55">
         <v>119</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="55">
         <v>120</v>
       </c>
@@ -17167,7 +17167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="55">
         <v>121</v>
       </c>
@@ -17264,7 +17264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="55">
         <v>122</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="55">
         <v>123</v>
       </c>
@@ -17458,7 +17458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="55">
         <v>124</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="55">
         <v>125</v>
       </c>
@@ -17652,7 +17652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="55">
         <v>126</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="55">
         <v>127</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="55">
         <v>128</v>
       </c>
@@ -17943,7 +17943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="55">
         <v>129</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="55">
         <v>130</v>
       </c>
@@ -18137,7 +18137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="55">
         <v>131</v>
       </c>
@@ -18234,7 +18234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="55">
         <v>132</v>
       </c>
@@ -18331,7 +18331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="55">
         <v>133</v>
       </c>
@@ -18428,7 +18428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="55">
         <v>134</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="55">
         <v>135</v>
       </c>
@@ -18622,7 +18622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="55">
         <v>136</v>
       </c>
@@ -18719,7 +18719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="55">
         <v>137</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="55">
         <v>138</v>
       </c>
@@ -18917,7 +18917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="55">
         <v>139</v>
       </c>
@@ -19016,7 +19016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="55">
         <v>140</v>
       </c>
@@ -19115,7 +19115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="55">
         <v>141</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="55">
         <v>142</v>
       </c>
@@ -19313,7 +19313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="55">
         <v>143</v>
       </c>
@@ -19412,7 +19412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="55">
         <v>144</v>
       </c>
@@ -19511,7 +19511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="55">
         <v>145</v>
       </c>
@@ -19610,7 +19610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="55">
         <v>146</v>
       </c>
@@ -19621,10 +19621,10 @@
         <v>1199</v>
       </c>
       <c r="D146" s="37" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E146" s="37" t="s">
         <v>1200</v>
-      </c>
-      <c r="E146" s="37" t="s">
-        <v>1201</v>
       </c>
       <c r="F146" s="37" t="s">
         <v>1202</v>
@@ -19650,11 +19650,11 @@
       </c>
       <c r="M146" s="63" t="str">
         <f t="shared" si="220"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N146" s="63" t="str">
         <f t="shared" si="220"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O146" s="63" t="str">
         <f t="shared" si="220"/>
@@ -19680,11 +19680,11 @@
       </c>
       <c r="U146" s="45" t="str">
         <f t="shared" si="167"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V146" s="64" t="str">
         <f t="shared" si="167"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W146" s="45" t="s">
         <v>670</v>
@@ -19758,14 +19758,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="22"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -19830,7 +19830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -19904,16 +19904,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.3046875" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -19963,64 +19963,64 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AEE4CE-BFBA-437F-8898-28AC97CBFC26}">
   <dimension ref="A1:BA161"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.3046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.84375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.84375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="109.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="94.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="109.84375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="94.15234375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.69140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.84375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="4.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -20503,7 +20503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -20825,7 +20825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -21147,7 +21147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -21308,7 +21308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -21791,7 +21791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -21952,7 +21952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -22435,7 +22435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -22596,7 +22596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -22757,7 +22757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -23079,7 +23079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -23401,7 +23401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -23723,7 +23723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -23884,7 +23884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -24045,7 +24045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -24367,7 +24367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -24528,7 +24528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -24689,7 +24689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -24850,7 +24850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -25011,7 +25011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -25172,7 +25172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -25333,7 +25333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -25494,7 +25494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -25655,7 +25655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -25816,7 +25816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -25977,7 +25977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -26299,7 +26299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -26460,7 +26460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -26621,7 +26621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -26782,7 +26782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -26943,7 +26943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -27104,7 +27104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -27265,7 +27265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -27426,7 +27426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -27587,7 +27587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -27748,7 +27748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -27909,7 +27909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -28070,7 +28070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -28231,7 +28231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -28553,7 +28553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -28714,7 +28714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -28875,7 +28875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -29036,7 +29036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -29197,7 +29197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -29358,7 +29358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -29519,7 +29519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -29680,7 +29680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -29841,7 +29841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="16">
         <v>62</v>
       </c>
@@ -30002,7 +30002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="16">
         <v>63</v>
       </c>
@@ -30163,7 +30163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="16">
         <v>64</v>
       </c>
@@ -30324,7 +30324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="16">
         <v>65</v>
       </c>
@@ -30485,7 +30485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="16">
         <v>66</v>
       </c>
@@ -30646,7 +30646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="16">
         <v>67</v>
       </c>
@@ -30807,7 +30807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="16">
         <v>68</v>
       </c>
@@ -30968,7 +30968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="16">
         <v>69</v>
       </c>
@@ -31129,7 +31129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="16">
         <v>70</v>
       </c>
@@ -31290,7 +31290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="16">
         <v>71</v>
       </c>
@@ -31451,7 +31451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="16">
         <v>72</v>
       </c>
@@ -31612,7 +31612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="16">
         <v>73</v>
       </c>
@@ -31773,7 +31773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="16">
         <v>74</v>
       </c>
@@ -31934,7 +31934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="16">
         <v>75</v>
       </c>
@@ -32095,7 +32095,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="16">
         <v>76</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="16">
         <v>77</v>
       </c>
@@ -32417,7 +32417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="16">
         <v>78</v>
       </c>
@@ -32578,7 +32578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="16">
         <v>79</v>
       </c>
@@ -32739,7 +32739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="16">
         <v>80</v>
       </c>
@@ -32900,7 +32900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="16">
         <v>81</v>
       </c>
@@ -33061,7 +33061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="16">
         <v>82</v>
       </c>
@@ -33222,7 +33222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="16">
         <v>83</v>
       </c>
@@ -33383,7 +33383,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16">
         <v>84</v>
       </c>
@@ -33544,7 +33544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="16">
         <v>85</v>
       </c>
@@ -33705,7 +33705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="16">
         <v>86</v>
       </c>
@@ -33866,7 +33866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16">
         <v>87</v>
       </c>
@@ -34027,7 +34027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16">
         <v>88</v>
       </c>
@@ -34188,7 +34188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16">
         <v>89</v>
       </c>
@@ -34349,7 +34349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16">
         <v>90</v>
       </c>
@@ -34510,7 +34510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16">
         <v>91</v>
       </c>
@@ -34671,7 +34671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16">
         <v>92</v>
       </c>
@@ -34832,7 +34832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16">
         <v>93</v>
       </c>
@@ -34993,7 +34993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16">
         <v>94</v>
       </c>
@@ -35154,7 +35154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="16">
         <v>95</v>
       </c>
@@ -35315,7 +35315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="16">
         <v>96</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16">
         <v>97</v>
       </c>
@@ -35637,7 +35637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16">
         <v>98</v>
       </c>
@@ -35798,7 +35798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16">
         <v>99</v>
       </c>
@@ -35959,7 +35959,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16">
         <v>100</v>
       </c>
@@ -36120,7 +36120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16">
         <v>101</v>
       </c>
@@ -36281,7 +36281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16">
         <v>102</v>
       </c>
@@ -36442,7 +36442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="16">
         <v>103</v>
       </c>
@@ -36603,7 +36603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="16">
         <v>104</v>
       </c>
@@ -36764,7 +36764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="16">
         <v>105</v>
       </c>
@@ -36925,7 +36925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="16">
         <v>106</v>
       </c>
@@ -37086,7 +37086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="16">
         <v>107</v>
       </c>
@@ -37247,7 +37247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="16">
         <v>108</v>
       </c>
@@ -37408,7 +37408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="16">
         <v>109</v>
       </c>
@@ -37569,7 +37569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="16">
         <v>110</v>
       </c>
@@ -37730,7 +37730,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="16">
         <v>111</v>
       </c>
@@ -37891,7 +37891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="16">
         <v>112</v>
       </c>
@@ -38052,7 +38052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="16">
         <v>113</v>
       </c>
@@ -38213,7 +38213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="16">
         <v>114</v>
       </c>
@@ -38374,7 +38374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="16">
         <v>115</v>
       </c>
@@ -38535,7 +38535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="16">
         <v>116</v>
       </c>
@@ -38696,7 +38696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="16">
         <v>117</v>
       </c>
@@ -38857,7 +38857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="16">
         <v>118</v>
       </c>
@@ -39018,7 +39018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="16">
         <v>119</v>
       </c>
@@ -39179,7 +39179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="16">
         <v>120</v>
       </c>
@@ -39340,7 +39340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="16">
         <v>121</v>
       </c>
@@ -39501,7 +39501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="16">
         <v>122</v>
       </c>
@@ -39662,7 +39662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="16">
         <v>123</v>
       </c>
@@ -39823,7 +39823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="16">
         <v>124</v>
       </c>
@@ -39984,7 +39984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="16">
         <v>125</v>
       </c>
@@ -40145,7 +40145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="16">
         <v>126</v>
       </c>
@@ -40306,7 +40306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="16">
         <v>127</v>
       </c>
@@ -40467,7 +40467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="16">
         <v>128</v>
       </c>
@@ -40628,7 +40628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="16">
         <v>129</v>
       </c>
@@ -40789,7 +40789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="16">
         <v>130</v>
       </c>
@@ -40950,7 +40950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="16">
         <v>131</v>
       </c>
@@ -41111,7 +41111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="16">
         <v>132</v>
       </c>
@@ -41272,7 +41272,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="16">
         <v>133</v>
       </c>
@@ -41433,7 +41433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="16">
         <v>134</v>
       </c>
@@ -41594,7 +41594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="16">
         <v>135</v>
       </c>
@@ -41755,7 +41755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="16">
         <v>136</v>
       </c>
@@ -41916,7 +41916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="16">
         <v>137</v>
       </c>
@@ -42077,7 +42077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="16">
         <v>138</v>
       </c>
@@ -42238,7 +42238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="16">
         <v>139</v>
       </c>
@@ -42399,7 +42399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="16">
         <v>140</v>
       </c>
@@ -42560,7 +42560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="16">
         <v>141</v>
       </c>
@@ -42721,7 +42721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="16">
         <v>142</v>
       </c>
@@ -42882,7 +42882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="16">
         <v>143</v>
       </c>
@@ -43043,7 +43043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="16">
         <v>144</v>
       </c>
@@ -43204,7 +43204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="16">
         <v>145</v>
       </c>
@@ -43365,7 +43365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="16">
         <v>146</v>
       </c>
@@ -43526,7 +43526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="16">
         <v>147</v>
       </c>
@@ -43687,7 +43687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="16">
         <v>148</v>
       </c>
@@ -43848,7 +43848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="16">
         <v>149</v>
       </c>
@@ -44009,7 +44009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="16">
         <v>150</v>
       </c>
@@ -44170,7 +44170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="16">
         <v>151</v>
       </c>
@@ -44331,7 +44331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="16">
         <v>152</v>
       </c>
@@ -44492,7 +44492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="16">
         <v>153</v>
       </c>
@@ -44653,7 +44653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="16">
         <v>154</v>
       </c>
@@ -44814,7 +44814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="16">
         <v>155</v>
       </c>
@@ -44975,7 +44975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="16">
         <v>156</v>
       </c>
@@ -45136,7 +45136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="16">
         <v>157</v>
       </c>
@@ -45298,7 +45298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="16">
         <v>158</v>
       </c>
@@ -45460,7 +45460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="16">
         <v>159</v>
       </c>
@@ -45622,7 +45622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="16">
         <v>160</v>
       </c>
@@ -45784,7 +45784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:53" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="16">
         <v>161</v>
       </c>
